--- a/Assets/Resources/MasterData/ItemDropTable.xlsx
+++ b/Assets/Resources/MasterData/ItemDropTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1705292-285C-486C-89D0-9A466ED77F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9029E1D-2A86-492D-B3A5-A40B0C69F6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7755" yWindow="-13410" windowWidth="9675" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15195" yWindow="-13635" windowWidth="9675" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDropTable" sheetId="1" r:id="rId1"/>
@@ -424,10 +424,10 @@
         <v>100</v>
       </c>
       <c r="D2" s="2">
-        <v>-1</v>
+        <v>200</v>
       </c>
       <c r="E2" s="2">
-        <v>-1</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:5">

--- a/Assets/Resources/MasterData/ItemDropTable.xlsx
+++ b/Assets/Resources/MasterData/ItemDropTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9029E1D-2A86-492D-B3A5-A40B0C69F6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DDB976-B6A6-4C7B-8101-C71668573B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15195" yWindow="-13635" windowWidth="9675" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDropTable" sheetId="1" r:id="rId1"/>
@@ -427,7 +427,7 @@
         <v>200</v>
       </c>
       <c r="E2" s="2">
-        <v>300</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -444,7 +444,7 @@
         <v>200</v>
       </c>
       <c r="E3" s="2">
-        <v>-1</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -458,10 +458,10 @@
         <v>300</v>
       </c>
       <c r="D4" s="2">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E4" s="2">
-        <v>500</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
